--- a/outputs/daily/predictions_2026-06-21.xlsx
+++ b/outputs/daily/predictions_2026-06-21.xlsx
@@ -1114,31 +1114,31 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.623687275909932</v>
+        <v>2.75355079782953</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6839765253331263</v>
+        <v>0.7191130034135281</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.866429655252228</v>
+        <v>0.8635801131515218</v>
       </c>
       <c r="O3" t="n">
-        <v>0.09459341713704394</v>
+        <v>0.096384392629313</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03897692761072813</v>
+        <v>0.0400354942191652</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6529891344964767</v>
+        <v>0.7070930346792417</v>
       </c>
       <c r="R3" t="n">
-        <v>2.677980791930342</v>
+        <v>2.914096286329612</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6820192080696575</v>
+        <v>0.7459037136703882</v>
       </c>
       <c r="T3" t="n">
         <v>0.7755988262041734</v>
@@ -1156,58 +1156,58 @@
         <v>0.4155949684269894</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.781234879025588</v>
+        <v>0.7918030991279034</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1514875550354872</v>
+        <v>0.1428068158865221</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.06727756593892537</v>
+        <v>0.06539008498557466</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6420767514019351</v>
+        <v>0.6740208043915253</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.3579232485980649</v>
+        <v>0.3259791956084747</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4660258000152984</v>
+        <v>0.486290156546005</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5339741999847016</v>
+        <v>0.5137098434539951</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.7811</v>
+        <v>0.791815</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.15216</v>
+        <v>0.1432</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.06673999999999999</v>
+        <v>0.064985</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.64291</v>
+        <v>0.674055</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.4671</v>
+        <v>0.486275</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.62325</v>
+        <v>2.75393</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.684995</v>
+        <v>0.716545</v>
       </c>
       <c r="AM3" t="n">
-        <v>3.308245</v>
+        <v>3.470475</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.8133401710287489</v>
+        <v>0.8148424092140453</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1403570687262733</v>
+        <v>0.1389032741359397</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.04630276024497791</v>
+        <v>0.04625431665001507</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>0.8133401710287489</v>
+        <v>0.8148424092140453</v>
       </c>
       <c r="AS3" t="b">
         <v>1</v>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>10.57156015995523</v>
+        <v>10.37512373861112</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1403570687262733</v>
+        <v>0.1389032741359397</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.04576365158922938</v>
+        <v>0.04251888150662667</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.4837931959147692</v>
+        <v>0.4411386568585955</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
@@ -1243,16 +1243,16 @@
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>10.57156015995523</v>
+        <v>10.37512373861112</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1403570687262733</v>
+        <v>0.1389032741359397</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.04576365158922938</v>
+        <v>0.04251888150662667</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.4837931959147692</v>
+        <v>0.4411386568585955</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="BE3" t="n">
-        <v>0.1259896128992682</v>
+        <v>0.1176682087156869</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1268,23 +1268,23 @@
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>0.1101857814202092</v>
+        <v>0.1080017966627504</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="BI3" t="n">
+        <v>0.0846167389758275</v>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="BI3" t="n">
-        <v>0.08947119590894925</v>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
       <c r="BK3" t="n">
-        <v>0.08617393765890705</v>
+        <v>0.07932051582573711</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>0.07536448791691003</v>
+        <v>0.07766549637220761</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="BO3" t="n">
-        <v>0.07227325817459894</v>
+        <v>0.07434710834193478</v>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="BQ3" t="n">
-        <v>0.07225810201935959</v>
+        <v>0.06760609823997345</v>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
@@ -1316,23 +1316,23 @@
         </is>
       </c>
       <c r="BS3" t="n">
-        <v>0.04943321200076615</v>
+        <v>0.05346397237487969</v>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="BU3" t="n">
+        <v>0.04094370789825062</v>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
           <t>0-0</t>
         </is>
       </c>
-      <c r="BU3" t="n">
-        <v>0.04317393419794729</v>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>5-0</t>
-        </is>
-      </c>
       <c r="BW3" t="n">
-        <v>0.03792448557224976</v>
+        <v>0.03718466811381053</v>
       </c>
     </row>
     <row r="4">
@@ -1385,31 +1385,31 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1.670669599666164</v>
+        <v>1.680935123244319</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9342222274762652</v>
+        <v>0.9349567038981108</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6678765709541069</v>
+        <v>0.6647474650861844</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2065260460173231</v>
+        <v>0.2124066683014411</v>
       </c>
       <c r="P4" t="n">
-        <v>0.12559738302857</v>
+        <v>0.1228458666123745</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.528687092186665</v>
+        <v>0.5328523481675136</v>
       </c>
       <c r="R4" t="n">
-        <v>2.014694762737247</v>
+        <v>2.033359351061164</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7753052372627527</v>
+        <v>0.7766406489388356</v>
       </c>
       <c r="T4" t="n">
         <v>0.471668657388788</v>
@@ -1427,58 +1427,58 @@
         <v>0.5045182925634963</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5354921416840951</v>
+        <v>0.5378447770270027</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2659715423212218</v>
+        <v>0.2648158040576685</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1985363159946831</v>
+        <v>0.1973394189153292</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4827969944830603</v>
+        <v>0.4855517811472027</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.5172030055169397</v>
+        <v>0.5144482188527972</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5044344642151121</v>
+        <v>0.5057885689579622</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.4955655357848879</v>
+        <v>0.4942114310420378</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.5363250000000001</v>
+        <v>0.538795</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.264955</v>
+        <v>0.263475</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.19872</v>
+        <v>0.19773</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.482615</v>
+        <v>0.485165</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.5036350000000001</v>
+        <v>0.50462</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.671335</v>
+        <v>1.681715</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.933705</v>
+        <v>0.93448</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.60504</v>
+        <v>2.616195</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.5661076938887424</v>
+        <v>0.5654442103773002</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.238875198655575</v>
+        <v>0.2409385130033339</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.1950171074556827</v>
+        <v>0.193617276619366</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="AR4" t="n">
-        <v>0.5661076938887424</v>
+        <v>0.5654442103773002</v>
       </c>
       <c r="AS4" t="b">
         <v>1</v>
@@ -1497,16 +1497,16 @@
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>7.961949332754227</v>
+        <v>8.140282026381733</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.1950171074556827</v>
+        <v>0.193617276619366</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.06941972442711267</v>
+        <v>0.07077141000699146</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.5527163285824319</v>
+        <v>0.5760992368616049</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>7.961949332754227</v>
+        <v>8.140282026381733</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.1950171074556827</v>
+        <v>0.193617276619366</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.06941972442711267</v>
+        <v>0.07077141000699146</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.5527163285824319</v>
+        <v>0.5760992368616049</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="BE4" t="n">
-        <v>0.1268948447034176</v>
+        <v>0.1263771232667802</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="BG4" t="n">
-        <v>0.111945377830772</v>
+        <v>0.1113920413517803</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="BI4" t="n">
-        <v>0.1031482043007048</v>
+        <v>0.1032773858005777</v>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>0.09636334518198128</v>
+        <v>0.09655988421532168</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
@@ -1563,39 +1563,39 @@
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>0.08544714159444301</v>
+        <v>0.08459151434012031</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.05786752840968173</v>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="BO4" t="n">
-        <v>0.05751363448115863</v>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>3-0</t>
-        </is>
-      </c>
       <c r="BQ4" t="n">
-        <v>0.0574421897284474</v>
+        <v>0.05685901598115099</v>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.05410363362464631</v>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="BS4" t="n">
-        <v>0.05388544748821889</v>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
       <c r="BU4" t="n">
-        <v>0.05366377043922436</v>
+        <v>0.05370779028074276</v>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="BW4" t="n">
-        <v>0.04501238949148739</v>
+        <v>0.04513965553737019</v>
       </c>
     </row>
     <row r="5">
@@ -1656,31 +1656,31 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1.802536779502844</v>
+        <v>1.799077806864669</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6896913505110204</v>
+        <v>0.682150323149195</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6544454609114809</v>
+        <v>0.6503776269572461</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2286539231085537</v>
+        <v>0.238271381699194</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1169006159799654</v>
+        <v>0.11135099134356</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.426051518637363</v>
+        <v>0.4209132515348546</v>
       </c>
       <c r="R5" t="n">
-        <v>1.729045896532177</v>
+        <v>1.72275685537186</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6509541034678226</v>
+        <v>0.6372431446281401</v>
       </c>
       <c r="T5" t="n">
         <v>0.6780407440518693</v>
@@ -1698,58 +1698,58 @@
         <v>0.3936685051628153</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6302602648550499</v>
+        <v>0.6314974206365577</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2428783772013115</v>
+        <v>0.2429513349227181</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.126861357943639</v>
+        <v>0.1255512444407242</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4541900064323864</v>
+        <v>0.4513609410023401</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.5458099935676136</v>
+        <v>0.54863905899766</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4263985905165895</v>
+        <v>0.4229247521578132</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.5736014094834105</v>
+        <v>0.5770752478421868</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.6312</v>
+        <v>0.63224</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.241365</v>
+        <v>0.241475</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.127435</v>
+        <v>0.126285</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.45456</v>
+        <v>0.45176</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.42547</v>
+        <v>0.422255</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.803125</v>
+        <v>1.79951</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.68923</v>
+        <v>0.68268</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.492355</v>
+        <v>2.48219</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.656657510996509</v>
+        <v>0.6553396663601921</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.2262995825423808</v>
+        <v>0.2301648054089886</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.1170429064611101</v>
+        <v>0.1144955282308193</v>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="AR5" t="n">
-        <v>0.656657510996509</v>
+        <v>0.6553396663601921</v>
       </c>
       <c r="AS5" t="b">
         <v>1</v>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>2.347133987923084</v>
+        <v>2.375786450898167</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.4541900064323864</v>
+        <v>0.4513609410023401</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.02813848779502337</v>
+        <v>0.03044768946748544</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.06604480107245836</v>
+        <v>0.0723372080980067</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
@@ -1785,16 +1785,16 @@
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2.347133987923084</v>
+        <v>2.375786450898167</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.4541900064323864</v>
+        <v>0.4513609410023401</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.02813848779502337</v>
+        <v>0.03044768946748544</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.06604480107245836</v>
+        <v>0.0723372080980067</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="BE5" t="n">
-        <v>0.1388317071353604</v>
+        <v>0.1402113952714895</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="BG5" t="n">
-        <v>0.1343936424096908</v>
+        <v>0.135359132337774</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="BI5" t="n">
-        <v>0.1131285055222224</v>
+        <v>0.1129120742464789</v>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>0.09301010951979424</v>
+        <v>0.09390543523039883</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>0.09269013273363476</v>
+        <v>0.0923352758654072</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         </is>
       </c>
       <c r="BO5" t="n">
-        <v>0.08074982779160692</v>
+        <v>0.08117387031511565</v>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0556924577831257</v>
+        <v>0.055372781866727</v>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="BS5" t="n">
-        <v>0.04677079011159959</v>
+        <v>0.04679079733504962</v>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="BU5" t="n">
-        <v>0.03638863363322307</v>
+        <v>0.03650952714530883</v>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="BW5" t="n">
-        <v>0.03546534170677956</v>
+        <v>0.03501045815212793</v>
       </c>
     </row>
     <row r="6">
